--- a/data/Wohlen (AG)/investment_decision/Anglikon_district_investment_decision.xlsx
+++ b/data/Wohlen (AG)/investment_decision/Anglikon_district_investment_decision.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,32 +461,32 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>6.832440469385312</v>
+        <v>2.055226643905746</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -524,7 +524,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2.055226643905746</v>
+        <v>6.832440469385312</v>
       </c>
     </row>
     <row r="3">
@@ -549,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>6.832440469385312</v>
+        <v>3.259997429673818</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>3.259997429673818</v>
+        <v>6.832440469385312</v>
       </c>
     </row>
     <row r="4">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>6.832440469385312</v>
+        <v>4.023622139321716</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -598,7 +598,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>4.023622139321716</v>
+        <v>6.832440469385312</v>
       </c>
     </row>
     <row r="5">
@@ -623,7 +623,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>6.832440469385312</v>
+        <v>4.537264584863329</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -635,7 +635,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4.537264584863329</v>
+        <v>6.832440469385312</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>6.832440469385312</v>
+        <v>4.899576600824727</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>4.899576600824727</v>
+        <v>6.832440469385312</v>
       </c>
     </row>
     <row r="7">
@@ -680,7 +680,7 @@
         <v>46023</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2462010070660789</v>
+        <v>0.2469594657798744</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -694,22 +694,22 @@
         <v>6.832440469385312</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2462010070660789</v>
+        <v>0.2466340468394748</v>
       </c>
       <c r="G7" t="n">
-        <v>6.832440469385312</v>
+        <v>2.055226643905746</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2462010070660788</v>
+        <v>0.246828459305414</v>
       </c>
       <c r="I7" t="n">
         <v>2.055226643905746</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2462010070660788</v>
+        <v>0.2467226184048543</v>
       </c>
       <c r="K7" t="n">
-        <v>2.055226643905746</v>
+        <v>6.832440469385312</v>
       </c>
     </row>
     <row r="8">
@@ -717,7 +717,7 @@
         <v>47849</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2462010070660789</v>
+        <v>0.2469594657798744</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -731,22 +731,22 @@
         <v>6.832440469385312</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2462010070660789</v>
+        <v>0.2466340468394748</v>
       </c>
       <c r="G8" t="n">
-        <v>6.832440469385312</v>
+        <v>3.259997429673818</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2462010070660788</v>
+        <v>0.246828459305414</v>
       </c>
       <c r="I8" t="n">
         <v>3.259997429673818</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2462010070660788</v>
+        <v>0.2467226184048543</v>
       </c>
       <c r="K8" t="n">
-        <v>3.259997429673818</v>
+        <v>6.832440469385312</v>
       </c>
     </row>
     <row r="9">
@@ -754,7 +754,7 @@
         <v>49675</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2507645454508801</v>
+        <v>0.3649720710957249</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -768,22 +768,22 @@
         <v>6.832440469385312</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2508118794764953</v>
+        <v>0.3648733342284312</v>
       </c>
       <c r="G9" t="n">
-        <v>6.832440469385312</v>
+        <v>4.023622139321716</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2511513856128079</v>
+        <v>0.3644373626083655</v>
       </c>
       <c r="I9" t="n">
         <v>4.023622139321716</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2509534799985051</v>
+        <v>0.3655471153568113</v>
       </c>
       <c r="K9" t="n">
-        <v>4.023622139321716</v>
+        <v>6.832440469385312</v>
       </c>
     </row>
     <row r="10">
@@ -791,7 +791,7 @@
         <v>51502</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2583665108156671</v>
+        <v>0.3713218687874228</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -805,22 +805,22 @@
         <v>6.832440469385312</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2559415050118434</v>
+        <v>0.3711950313255283</v>
       </c>
       <c r="G10" t="n">
-        <v>6.832440469385312</v>
+        <v>4.537264584863329</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2559415050118435</v>
+        <v>0.3710094977755651</v>
       </c>
       <c r="I10" t="n">
         <v>4.537264584863329</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2583665108156671</v>
+        <v>0.3713205749809366</v>
       </c>
       <c r="K10" t="n">
-        <v>4.537264584863329</v>
+        <v>6.832440469385312</v>
       </c>
     </row>
     <row r="11">
@@ -828,7 +828,7 @@
         <v>53328</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2583665108156671</v>
+        <v>0.3713218687874228</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -842,22 +842,22 @@
         <v>6.832440469385312</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2559415050118434</v>
+        <v>0.3711950313255283</v>
       </c>
       <c r="G11" t="n">
-        <v>6.832440469385312</v>
+        <v>4.899576600824727</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2559415050118435</v>
+        <v>0.3710094977755651</v>
       </c>
       <c r="I11" t="n">
         <v>4.899576600824727</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2583665108156671</v>
+        <v>0.3713205749809366</v>
       </c>
       <c r="K11" t="n">
-        <v>4.899576600824727</v>
+        <v>6.832440469385312</v>
       </c>
     </row>
     <row r="12">
@@ -1043,746 +1043,6 @@
       </c>
       <c r="K16" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.01033430557209638</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Anglikon</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>175</v>
-      </c>
-      <c r="E17" t="n">
-        <v>4.449374638146136</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.01033430557209638</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4.449374638146136</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.01033430557209638</v>
-      </c>
-      <c r="I17" t="n">
-        <v>4.449374638146136</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.01033430557209638</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4.449374638146136</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.01033430557209638</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Anglikon</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>175</v>
-      </c>
-      <c r="E18" t="n">
-        <v>4.449374638146136</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.01033430557209638</v>
-      </c>
-      <c r="G18" t="n">
-        <v>4.449374638146136</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.01033430557209638</v>
-      </c>
-      <c r="I18" t="n">
-        <v>4.449374638146136</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.01033430557209638</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4.449374638146136</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.01054292446968729</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Anglikon</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>175</v>
-      </c>
-      <c r="E19" t="n">
-        <v>4.449374638146136</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.01054508831085827</v>
-      </c>
-      <c r="G19" t="n">
-        <v>4.449374638146136</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.01056060859137542</v>
-      </c>
-      <c r="I19" t="n">
-        <v>4.449374638146136</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.01055156147757865</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.449374638146136</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.01122774799775856</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Anglikon</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>175</v>
-      </c>
-      <c r="E20" t="n">
-        <v>4.449374638146136</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.01133261787775074</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4.449374638146136</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.011323427852565</v>
-      </c>
-      <c r="I20" t="n">
-        <v>4.449374638146136</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.0112317522734598</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4.449374638146136</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.01128464174629387</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Anglikon</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>175</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4.449374638146136</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.01138569251464169</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4.449374638146136</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.01137373524510949</v>
-      </c>
-      <c r="I21" t="n">
-        <v>4.449374638146136</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.0112820596660043</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.449374638146136</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Anglikon</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>8</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.8122752563530218</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.8122752563530218</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.0254094784621596</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.0254094784621596</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Anglikon</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.8122752563530218</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.8122752563530218</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.04740422649669234</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.04740422649669234</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Anglikon</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>8</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.8122752563530218</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.8122752563530218</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.06675467054559274</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.06675467054559274</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Anglikon</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.8122752563530218</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.8122752563530218</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.0840114150401025</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.0840114150401025</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Anglikon</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.8122752563530218</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.8122752563530218</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09957196509644654</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.09957196509644654</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Anglikon</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1.565831819475705</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1.565831819475705</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.04898212715597031</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.04898212715597031</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Anglikon</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1.565831819475705</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1.565831819475705</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09138164143940693</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.09138164143940693</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Anglikon</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1.565831819475705</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.565831819475705</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.1286837022565643</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.1286837022565643</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Anglikon</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1.565831819475705</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1.565831819475705</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.1619497157399566</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.1619497157399566</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Anglikon</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1.565831819475705</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1.565831819475705</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.191945956812427</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0.191945956812427</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Anglikon</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>300</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.02166067350274725</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.02166067350274725</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.000677586092324256</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.000677586092324256</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Anglikon</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>300</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.02166067350274725</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.02166067350274725</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.001264112706578463</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.001264112706578463</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Anglikon</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>300</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.02166067350274725</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.02166067350274725</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.001780124547882473</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.001780124547882473</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Anglikon</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>300</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.02166067350274725</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.02166067350274725</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.0022403044010694</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.0022403044010694</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Anglikon</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>300</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.02166067350274725</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.02166067350274725</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.002655252402571908</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.002655252402571908</v>
       </c>
     </row>
   </sheetData>
